--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
   <si>
     <t>Filename</t>
   </si>
@@ -808,721 +808,700 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9949,0.0002,0.0004,0.0028</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9225,0.0013,0.0032,0.0482</t>
-  </si>
-  <si>
-    <t>0.0013,0.0025,0.0005,0.9989</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9883,0.0010,0.0013,0.0037</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9887,0.0002,0.0002,0.0079</t>
+  </si>
+  <si>
+    <t>0.0008,0.0006,0.0007,0.9992</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0019,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0090,0.0009,0.9883,0.0003</t>
+  </si>
+  <si>
+    <t>0.0457,0.0010,0.9677,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0003,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.9916,0.0001,0.0080,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.9973,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9989,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0474,0.0001,0.9546,0.0004</t>
+  </si>
+  <si>
+    <t>0.7197,0.0002,0.3497,0.0009</t>
+  </si>
+  <si>
+    <t>0.0018,0.0002,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.0001,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.0072,0.0001,0.9927,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9990,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9989,0.0015</t>
+  </si>
+  <si>
+    <t>0.0528,0.9696,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9943,0.0009,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,1.0000,0.0121</t>
+  </si>
+  <si>
+    <t>0.0014,0.9694,0.1454,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0448,0.0023,0.9445,0.0040</t>
+  </si>
+  <si>
+    <t>0.1317,0.8787,0.0070,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.9902,0.0155,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.0018,0.9893,0.0009</t>
+  </si>
+  <si>
+    <t>0.0181,0.0006,0.9804,0.0008</t>
+  </si>
+  <si>
+    <t>0.2724,0.0011,0.7555,0.0005</t>
+  </si>
+  <si>
+    <t>0.0144,0.0000,0.9824,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0017,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0000,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.9435,0.0047,0.3528</t>
+  </si>
+  <si>
+    <t>0.0003,0.9952,0.0001,0.0024</t>
+  </si>
+  <si>
+    <t>0.0006,0.9974,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0196,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0001,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0000,0.9966,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0015,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.9965,0.0034,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0018,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9999,0.0010</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9956,0.8301,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0016,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9905,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.7486,0.0394,0.0961,0.0023</t>
+  </si>
+  <si>
+    <t>0.0178,0.0003,0.9783,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.8401,0.9263,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.2247,0.9807,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.1208,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9836,0.9703,0.0001</t>
+  </si>
+  <si>
+    <t>0.0118,0.0001,0.0010,0.9934</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0010,0.9995</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9937,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8123,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9912,0.9793,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.5147,0.9967,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9925,0.9526,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9761,0.9708,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0016,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0058,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9957,0.0056,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0024,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9988,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0024,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0037,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0057,0.9894,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.9975,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0857,0.9163,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.1849,0.0081,0.6636,0.0023</t>
+  </si>
+  <si>
+    <t>0.3096,0.0007,0.6897,0.0011</t>
+  </si>
+  <si>
+    <t>0.9270,0.0030,0.0463,0.0004</t>
+  </si>
+  <si>
+    <t>0.3057,0.0066,0.6190,0.0041</t>
+  </si>
+  <si>
+    <t>0.0003,0.0018,0.0000,0.9991</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9551,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9981,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.8980,0.0723,0.0116,0.0005</t>
+  </si>
+  <si>
+    <t>0.6206,0.4024,0.0046,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9329,0.9868,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.1951,0.9412,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0001,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9390,0.0012,0.0368,0.0017</t>
+  </si>
+  <si>
+    <t>0.0854,0.0000,0.9279,0.0003</t>
+  </si>
+  <si>
+    <t>0.9861,0.0002,0.0086,0.0003</t>
+  </si>
+  <si>
+    <t>0.0085,0.0000,0.0001,0.9971</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.8566,0.9557,0.0001</t>
+  </si>
+  <si>
+    <t>0.0037,0.9887,0.0027,0.0039</t>
+  </si>
+  <si>
+    <t>0.2629,0.5425,0.0439,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1525,0.0000,0.0015,0.8184</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0115,0.9970,0.0325</t>
+  </si>
+  <si>
+    <t>0.9982,0.0000,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9818,0.0003,0.0062,0.0015</t>
+  </si>
+  <si>
+    <t>0.1921,0.8114,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9656,0.0159,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.9733,0.0094,0.0055,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9856,0.0096,0.0022,0.0004</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9952,0.0002,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.0025,0.9930,0.0004</t>
-  </si>
-  <si>
-    <t>0.1536,0.0012,0.8687,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0002,0.9961,0.0007</t>
-  </si>
-  <si>
-    <t>0.9972,0.0000,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.9984,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0047,0.9939,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.9985,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9025,0.0002,0.1305,0.0008</t>
-  </si>
-  <si>
-    <t>0.9889,0.0000,0.0134,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0126,0.0006,0.9856,0.0002</t>
-  </si>
-  <si>
-    <t>0.0243,0.0000,0.9852,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0000,0.9960,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0009</t>
-  </si>
-  <si>
-    <t>0.4403,0.7669,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8510,0.0996,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0371</t>
-  </si>
-  <si>
-    <t>0.0020,0.9772,0.0488,0.0001</t>
-  </si>
-  <si>
-    <t>0.9943,0.0019,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0048,0.0031,0.9888,0.0033</t>
-  </si>
-  <si>
-    <t>0.0778,0.9227,0.0080,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9960,0.0203,0.0001</t>
-  </si>
-  <si>
-    <t>0.0072,0.0017,0.9818,0.0011</t>
-  </si>
-  <si>
-    <t>0.0046,0.0018,0.9835,0.0054</t>
-  </si>
-  <si>
-    <t>0.0097,0.0034,0.9797,0.0002</t>
-  </si>
-  <si>
-    <t>0.0201,0.0000,0.9758,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0013,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9979,0.0050,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9931,0.0006,0.2070</t>
-  </si>
-  <si>
-    <t>0.0004,0.9972,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.9990,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0092,0.9960,0.0002</t>
-  </si>
-  <si>
-    <t>0.0157,0.0000,0.9898,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9995,0.0006</t>
-  </si>
-  <si>
-    <t>0.9947,0.0063,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0023,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9998,0.0044</t>
-  </si>
-  <si>
-    <t>0.9983,0.0005,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9689,0.9620,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0083,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0007,0.9956,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.8938,0.9970,0.0001</t>
+    <t>0.3735,0.3228,0.0001,0.0044</t>
+  </si>
+  <si>
+    <t>0.1172,0.9138,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.9490,0.0980,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7696,0.0055,0.1380,0.0008</t>
+  </si>
+  <si>
+    <t>0.9896,0.0051,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9976,0.0012,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9636,0.0291,0.0045,0.0013</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0005,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0041,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0075,0.0001,0.9957,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0156,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9996,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.9991,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0002,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.9275,0.0023,0.0434,0.0013</t>
-  </si>
-  <si>
-    <t>0.0066,0.0004,0.9928,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.9886,0.9899,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.7990,0.9557,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0076,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.8860,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.0000,0.0010,0.9963</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0018,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.9860,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9121,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9945,0.0810,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.9157,0.9498,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9722,0.9843,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.6588,0.9226,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0001</t>
+    <t>0.0001,0.0001,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0008,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0700,0.0007,0.9429,0.0004</t>
+  </si>
+  <si>
+    <t>0.0074,0.0022,0.9877,0.0002</t>
+  </si>
+  <si>
+    <t>0.0259,0.0098,0.9476,0.0007</t>
+  </si>
+  <si>
+    <t>0.0050,0.2290,0.8087,0.0007</t>
+  </si>
+  <si>
+    <t>0.9427,0.0015,0.0571,0.0003</t>
+  </si>
+  <si>
+    <t>0.7755,0.0028,0.1476,0.0024</t>
+  </si>
+  <si>
+    <t>0.7042,0.0007,0.2054,0.0081</t>
+  </si>
+  <si>
+    <t>0.0172,0.9856,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9969,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.8385,0.2548,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7817,0.2700,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.8535,0.2199,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9188,0.0109,0.0277,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0000,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.8552,0.0007,0.0004,0.1107</t>
+  </si>
+  <si>
+    <t>0.3195,0.0008,0.7331,0.0007</t>
+  </si>
+  <si>
+    <t>0.0660,0.0002,0.9179,0.0051</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9971,0.0182</t>
+  </si>
+  <si>
+    <t>0.0167,0.0071,0.9555,0.0034</t>
+  </si>
+  <si>
+    <t>0.0030,0.0119,0.9937,0.0001</t>
+  </si>
+  <si>
+    <t>0.0502,0.0001,0.9586,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.0069,0.9938,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0026,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9986,0.0016,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0040,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0010,0.9994,0.0006</t>
+  </si>
+  <si>
+    <t>0.0123,0.0120,0.9675,0.0021</t>
+  </si>
+  <si>
+    <t>0.9714,0.0004,0.0069,0.0053</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.6368,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.9973,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0010,0.9957,0.0003</t>
+  </si>
+  <si>
+    <t>0.9927,0.0000,0.0097,0.0001</t>
+  </si>
+  <si>
+    <t>0.9217,0.0002,0.1166,0.0006</t>
+  </si>
+  <si>
+    <t>0.9970,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0028,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0017,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9977,0.0022,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9900,0.0135,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0001,0.0026,0.0002</t>
+    <t>0.9944,0.0062,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0014,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0011,0.9926,0.0008</t>
+  </si>
+  <si>
+    <t>0.0067,0.0092,0.9796,0.0013</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.9996,0.0001</t>
   </si>
   <si>
-    <t>0.0004,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.9948,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.9921,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8603,0.1528,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9673,0.0010,0.0213,0.0004</t>
-  </si>
-  <si>
-    <t>0.9598,0.0000,0.0757,0.0000</t>
-  </si>
-  <si>
-    <t>0.9265,0.0203,0.0114,0.0016</t>
-  </si>
-  <si>
-    <t>0.1054,0.0045,0.8382,0.0075</t>
-  </si>
-  <si>
-    <t>0.0001,0.0019,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9260,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9989,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8073,0.1839,0.0056,0.0003</t>
-  </si>
-  <si>
-    <t>0.9596,0.0281,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9445,0.9459,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.0375,0.9907,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.8721,0.0095,0.0402,0.0036</t>
-  </si>
-  <si>
-    <t>0.4484,0.0000,0.7085,0.0001</t>
-  </si>
-  <si>
-    <t>0.9932,0.0002,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0002,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0007,0.9137,0.8004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0096,0.9825,0.0015,0.0040</t>
-  </si>
-  <si>
-    <t>0.2666,0.7199,0.0070,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.3911,0.0000,0.0022,0.5420</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0100,0.9978,0.0139</t>
-  </si>
-  <si>
-    <t>0.9558,0.0000,0.0138,0.0080</t>
-  </si>
-  <si>
-    <t>0.9435,0.0003,0.0317,0.0020</t>
-  </si>
-  <si>
-    <t>0.0259,0.9678,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0012,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.4218,0.2609,0.0520,0.0002</t>
-  </si>
-  <si>
-    <t>0.9903,0.0042,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0008,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9959,0.0025,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7890,0.0980,0.0001,0.0020</t>
-  </si>
-  <si>
-    <t>0.2217,0.8472,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.4237,0.7258,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9177,0.0328,0.0167,0.0003</t>
-  </si>
-  <si>
-    <t>0.9615,0.0290,0.0047,0.0009</t>
-  </si>
-  <si>
-    <t>0.9901,0.0072,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9538,0.0577,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0018,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9951,0.0013,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0013,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0307,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0060,0.0004,0.9929,0.0001</t>
-  </si>
-  <si>
-    <t>0.0070,0.0007,0.9936,0.0001</t>
-  </si>
-  <si>
-    <t>0.0601,0.0142,0.8576,0.0031</t>
-  </si>
-  <si>
-    <t>0.1340,0.0437,0.6748,0.0004</t>
-  </si>
-  <si>
-    <t>0.0389,0.8273,0.0183,0.0012</t>
-  </si>
-  <si>
-    <t>0.2690,0.0021,0.7788,0.0004</t>
-  </si>
-  <si>
-    <t>0.9748,0.0008,0.0112,0.0015</t>
-  </si>
-  <si>
-    <t>0.1513,0.0046,0.8123,0.0011</t>
-  </si>
-  <si>
-    <t>0.0761,0.9519,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.9975,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.6761,0.3720,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9799,0.0202,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.2823,0.7930,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9680,0.0106,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.5932,0.0050,0.0296,0.1378</t>
-  </si>
-  <si>
-    <t>0.9778,0.0007,0.0137,0.0002</t>
-  </si>
-  <si>
-    <t>0.7654,0.0003,0.3111,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.0002,0.9978,0.0006</t>
-  </si>
-  <si>
-    <t>0.0039,0.0040,0.9884,0.0010</t>
-  </si>
-  <si>
-    <t>0.0079,0.0134,0.9805,0.0005</t>
-  </si>
-  <si>
-    <t>0.0034,0.0001,0.9952,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0023,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0027,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9943,0.0045,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0008,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9996,0.0005</t>
-  </si>
-  <si>
-    <t>0.0358,0.8539,0.0557,0.0004</t>
-  </si>
-  <si>
-    <t>0.9374,0.0003,0.0021,0.0499</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.3052,0.9979,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0008,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.0052,0.0011,0.9886,0.0008</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8273,0.0001,0.2900,0.0001</t>
-  </si>
-  <si>
-    <t>0.9945,0.0001,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0074,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9546,0.0312,0.0068,0.0003</t>
-  </si>
-  <si>
-    <t>0.9917,0.0135,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0055,0.0099,0.9844,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0024,0.9929,0.0006</t>
-  </si>
-  <si>
-    <t>0.0046,0.0167,0.9573,0.0027</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.2844,0.0001,0.6907,0.0030</t>
-  </si>
-  <si>
-    <t>0.0013,0.0004,0.9964,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9969,0.0015</t>
-  </si>
-  <si>
-    <t>0.9927,0.0000,0.0017,0.0033</t>
-  </si>
-  <si>
-    <t>0.0120,0.0004,0.0000,0.9975</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.0018,0.9986</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.7700,0.0003,0.0004,0.2414</t>
+    <t>0.6442,0.0000,0.3540,0.0018</t>
+  </si>
+  <si>
+    <t>0.0043,0.0001,0.9947,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9993,0.0015</t>
+  </si>
+  <si>
+    <t>0.9230,0.0000,0.0010,0.0891</t>
+  </si>
+  <si>
+    <t>0.0047,0.0001,0.0000,0.9989</t>
+  </si>
+  <si>
+    <t>0.0243,0.0000,0.0001,0.9928</t>
+  </si>
+  <si>
+    <t>0.6872,0.0001,0.0003,0.5294</t>
   </si>
 </sst>
 </file>
@@ -1908,7 +1887,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1922,7 +1901,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1936,7 +1915,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1950,7 +1929,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1964,7 +1943,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1978,7 +1957,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1992,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2006,7 +1985,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2020,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2034,7 +2013,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2062,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2076,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2090,7 +2069,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2104,7 +2083,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2118,7 +2097,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2132,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2146,7 +2125,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2160,7 +2139,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2174,7 +2153,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2188,7 +2167,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2202,7 +2181,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2213,10 +2192,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2230,7 +2209,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2244,7 +2223,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2258,7 +2237,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2272,7 +2251,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2286,7 +2265,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2300,7 +2279,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2314,7 +2293,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2328,7 +2307,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2342,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2356,7 +2335,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2370,7 +2349,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2384,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2398,7 +2377,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2412,7 +2391,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2426,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2440,7 +2419,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2454,7 +2433,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2468,7 +2447,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2482,7 +2461,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2496,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2510,7 +2489,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2524,7 +2503,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2538,7 +2517,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2552,7 +2531,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2566,7 +2545,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2580,7 +2559,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2594,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2608,7 +2587,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2622,7 +2601,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2636,7 +2615,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2650,7 +2629,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2664,7 +2643,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2678,7 +2657,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2692,7 +2671,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2706,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2720,7 +2699,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2734,7 +2713,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2748,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2762,7 +2741,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2776,7 +2755,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2790,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2804,7 +2783,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2818,7 +2797,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2832,7 +2811,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2846,7 +2825,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2860,7 +2839,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2874,7 +2853,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2888,7 +2867,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2902,7 +2881,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2913,10 +2892,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2930,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2944,7 +2923,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2958,7 +2937,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2972,7 +2951,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2986,7 +2965,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>265</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3000,7 +2979,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3014,7 +2993,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3028,7 +3007,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3042,7 +3021,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3056,7 +3035,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3067,10 +3046,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3084,7 +3063,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3098,7 +3077,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3112,7 +3091,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3126,7 +3105,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3140,7 +3119,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3154,7 +3133,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3168,7 +3147,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>269</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3182,7 +3161,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3196,7 +3175,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3210,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3252,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>273</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3266,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>273</v>
+        <v>357</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3294,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3308,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3322,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3336,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>359</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3350,7 +3329,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3364,7 +3343,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3378,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3392,7 +3371,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3406,7 +3385,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3420,7 +3399,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3434,7 +3413,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3448,7 +3427,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3462,7 +3441,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3476,7 +3455,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3487,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>370</v>
@@ -3501,7 +3480,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
         <v>371</v>
@@ -3515,7 +3494,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>372</v>
@@ -3574,7 +3553,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3588,7 +3567,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3602,7 +3581,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3616,7 +3595,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3630,7 +3609,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3644,7 +3623,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3658,7 +3637,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3672,7 +3651,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3686,7 +3665,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3700,7 +3679,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3714,7 +3693,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3728,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>386</v>
+        <v>357</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3742,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3756,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>388</v>
+        <v>358</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3770,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3784,7 +3763,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3798,7 +3777,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3812,7 +3791,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3826,7 +3805,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3840,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>268</v>
+        <v>391</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3854,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3868,7 +3847,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3882,7 +3861,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3896,7 +3875,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3910,7 +3889,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3924,7 +3903,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>342</v>
+        <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3938,7 +3917,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>398</v>
+        <v>341</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3952,7 +3931,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3966,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3980,7 +3959,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3994,7 +3973,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>268</v>
+        <v>357</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4008,7 +3987,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4022,7 +4001,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4036,7 +4015,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4050,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4064,7 +4043,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4078,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4092,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4106,7 +4085,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4120,7 +4099,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4134,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4148,7 +4127,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4162,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4176,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4190,7 +4169,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4204,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4218,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>417</v>
+        <v>363</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4232,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4246,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4260,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4274,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>421</v>
+        <v>360</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4288,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4299,10 +4278,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4316,7 +4295,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4327,10 +4306,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4344,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4358,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4372,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4386,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4400,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4414,7 +4393,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4428,7 +4407,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4442,7 +4421,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4456,7 +4435,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4470,7 +4449,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4484,7 +4463,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4498,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4512,7 +4491,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4526,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4540,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4554,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4568,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4582,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4593,10 +4572,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4607,10 +4586,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4624,7 +4603,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4635,10 +4614,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4652,7 +4631,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4666,7 +4645,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4680,7 +4659,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4694,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4705,10 +4684,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4722,7 +4701,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4736,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4750,7 +4729,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4761,10 +4740,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4775,10 +4754,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4792,7 +4771,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4806,7 +4785,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4820,7 +4799,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4834,7 +4813,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4848,7 +4827,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4862,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4876,7 +4855,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4890,7 +4869,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4904,7 +4883,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4918,7 +4897,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4932,7 +4911,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4946,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4960,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>268</v>
+        <v>357</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4974,7 +4953,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4985,10 +4964,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5002,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5016,7 +4995,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5030,7 +5009,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5041,10 +5020,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5058,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>475</v>
+        <v>433</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5072,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5086,7 +5065,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>315</v>
+        <v>471</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5100,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5114,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5128,7 +5107,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5142,7 +5121,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5156,7 +5135,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5170,7 +5149,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5184,7 +5163,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5198,7 +5177,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5212,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5226,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>463</v>
+        <v>353</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5240,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5254,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5268,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5282,7 +5261,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5296,7 +5275,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5310,7 +5289,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5324,7 +5303,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5338,7 +5317,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5349,10 +5328,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5366,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5380,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5394,7 +5373,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5408,7 +5387,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5422,7 +5401,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5436,7 +5415,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>500</v>
+        <v>341</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5450,7 +5429,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>501</v>
+        <v>341</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5461,10 +5440,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D256" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
